--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F289A915-72A7-4E57-BA6E-1519D99A85FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1630B34-0C96-44E7-8183-CFED813753E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="0" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Component list</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Field=TotalQuantity</t>
-  </si>
-  <si>
     <t>Column=Designator</t>
   </si>
   <si>
@@ -89,7 +86,31 @@
     <t>Column=Comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Column=ComponentLink1URL </t>
+    <t>Column=Alternate Part No</t>
+  </si>
+  <si>
+    <t>Column=LCSC/Part No</t>
+  </si>
+  <si>
+    <t>Column=Quantity/5 Boards</t>
+  </si>
+  <si>
+    <t>Column=LCSC/MOQ/5 Boards</t>
+  </si>
+  <si>
+    <t>Column=Links</t>
+  </si>
+  <si>
+    <t>Column=Unit Cost/5 Boards</t>
+  </si>
+  <si>
+    <t>Column=Total Cost/5 Boards</t>
+  </si>
+  <si>
+    <t>Column=Remarks</t>
+  </si>
+  <si>
+    <t>Column=Reviewer Remarks</t>
   </si>
 </sst>
 </file>
@@ -99,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,21 +192,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -230,6 +236,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -268,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -335,21 +349,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -425,36 +424,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -466,11 +435,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -479,7 +450,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -487,6 +471,82 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -495,138 +555,185 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,13 +762,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -969,256 +1076,414 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="29" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" customWidth="1"/>
-    <col min="10" max="10" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="29.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.85546875" customWidth="1"/>
+    <col min="18" max="18" width="29.42578125" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="31"/>
+      <c r="B1" s="23"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="49"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="54"/>
     </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="4"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="5"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="50"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="55"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="7"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="51"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="56"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="6"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="51"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="56"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="51"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="56"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="51"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="56"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="51"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="56"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="I9" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="K9" s="34" t="s">
         <v>10</v>
       </c>
+      <c r="L9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="35" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="37">
+      <c r="B10" s="65">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="49"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="37">
+      <c r="B11" s="65">
         <f t="shared" ref="B11:B13" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="50"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="37">
+      <c r="B12" s="65">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="13"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="63"/>
+      <c r="S12" s="51"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="37">
+      <c r="B13" s="66">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="52"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="41" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47" t="s">
-        <v>13</v>
-      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="58"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="28"/>
+      <c r="C15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="46"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="59"/>
+      <c r="S15" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="J3:J8"/>
+  <mergeCells count="3">
+    <mergeCell ref="J1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="R14:S15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1630B34-0C96-44E7-8183-CFED813753E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD14786-97DB-4ECA-9AA0-579776306EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="0" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Component list</t>
   </si>
@@ -86,12 +86,6 @@
     <t>Column=Comment</t>
   </si>
   <si>
-    <t>Column=Alternate Part No</t>
-  </si>
-  <si>
-    <t>Column=LCSC/Part No</t>
-  </si>
-  <si>
     <t>Column=Quantity/5 Boards</t>
   </si>
   <si>
@@ -111,6 +105,15 @@
   </si>
   <si>
     <t>Column=Reviewer Remarks</t>
+  </si>
+  <si>
+    <t>Column=Item Type</t>
+  </si>
+  <si>
+    <t>Column=Alternate Part Number</t>
+  </si>
+  <si>
+    <t>Column=LCSC/Part Number</t>
   </si>
 </sst>
 </file>
@@ -120,7 +123,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,12 +195,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
@@ -245,6 +242,19 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -282,7 +292,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -456,16 +466,29 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -476,9 +499,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -488,56 +509,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -549,13 +520,24 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -569,38 +551,38 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -618,7 +600,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -628,28 +610,28 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -657,40 +639,69 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -705,34 +716,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -762,13 +755,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -799,7 +792,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13315950" y="600967"/>
+          <a:off x="29927550" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1076,60 +1069,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="29.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.85546875" customWidth="1"/>
-    <col min="18" max="18" width="29.42578125" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.42578125" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="23"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="54"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="63"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="12"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="4"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -1140,21 +1137,22 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="3"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="43"/>
+      <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="5"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1165,24 +1163,25 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="55"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="64"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="43"/>
+      <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="7"/>
+      <c r="H4" s="16"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="7"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
@@ -1190,21 +1189,22 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="56"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="65"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="43"/>
+      <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="18"/>
       <c r="G5" s="18"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="18"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -1215,17 +1215,18 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="56"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="65"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="26"/>
-      <c r="C6" s="19"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="19"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="18"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="20"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="6"/>
+      <c r="H6" s="18"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -1236,17 +1237,18 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="56"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="65"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="21"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="21"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="21"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
@@ -1257,17 +1259,18 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="56"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="65"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="31"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="31"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="21"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="8"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
@@ -1278,212 +1281,197 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="56"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="65"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="F9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="G9" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="H9" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="33" t="s">
+      <c r="N9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="33" t="s">
+      <c r="P9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="33" t="s">
+      <c r="Q9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="33" t="s">
+      <c r="R9" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="33" t="s">
+      <c r="S9" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="33" t="s">
+      <c r="T9" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="R9" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="65">
+      <c r="B10" s="41">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="61"/>
-      <c r="S10" s="49"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="53"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="65">
-        <f t="shared" ref="B11:B13" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="41">
+        <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="62"/>
-      <c r="S11" s="50"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="57"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="65">
+      <c r="B12" s="41">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="51"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="61"/>
     </row>
-    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="66">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="52"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="67"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="57"/>
-      <c r="S14" s="58"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="9" t="s">
+      <c r="B14" s="28"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="60"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="J1:S1"/>
-    <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R14:S15"/>
+    <mergeCell ref="K1:T1"/>
+    <mergeCell ref="T3:T8"/>
+    <mergeCell ref="S13:T14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD14786-97DB-4ECA-9AA0-579776306EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Component list</t>
   </si>
@@ -86,21 +85,9 @@
     <t>Column=Comment</t>
   </si>
   <si>
-    <t>Column=Quantity/5 Boards</t>
-  </si>
-  <si>
-    <t>Column=LCSC/MOQ/5 Boards</t>
-  </si>
-  <si>
     <t>Column=Links</t>
   </si>
   <si>
-    <t>Column=Unit Cost/5 Boards</t>
-  </si>
-  <si>
-    <t>Column=Total Cost/5 Boards</t>
-  </si>
-  <si>
     <t>Column=Remarks</t>
   </si>
   <si>
@@ -114,12 +101,24 @@
   </si>
   <si>
     <t>Column=LCSC/Part Number</t>
+  </si>
+  <si>
+    <t>Column=Quantity (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=MOQ (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=Total Cost (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=Unit Cost (5 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -755,13 +754,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -771,7 +770,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1067,9 +1066,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="29" customWidth="1"/>
@@ -1078,21 +1077,21 @@
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.42578125" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.42578125" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1111,10 +1110,9 @@
       <c r="P1" s="62"/>
       <c r="Q1" s="62"/>
       <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="63"/>
+      <c r="S1" s="63"/>
     </row>
-    <row r="2" spans="1:20" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="24"/>
       <c r="C2" s="42"/>
@@ -1126,8 +1124,8 @@
         <v>1</v>
       </c>
       <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1137,10 +1135,9 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="25"/>
       <c r="C3" s="43"/>
@@ -1152,8 +1149,8 @@
         <v>3</v>
       </c>
       <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -1163,10 +1160,9 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="64"/>
+      <c r="S3" s="64"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25"/>
       <c r="C4" s="43"/>
@@ -1178,8 +1174,8 @@
         <v>5</v>
       </c>
       <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="16"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="6"/>
@@ -1189,10 +1185,9 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="65"/>
+      <c r="S4" s="65"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
       <c r="C5" s="43"/>
@@ -1204,8 +1199,8 @@
         <v>7</v>
       </c>
       <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="18"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -1215,10 +1210,9 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="65"/>
+      <c r="S5" s="65"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="26"/>
       <c r="C6" s="44"/>
@@ -1226,8 +1220,8 @@
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="18"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -1237,10 +1231,9 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="65"/>
+      <c r="S6" s="65"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="27"/>
       <c r="C7" s="45"/>
@@ -1248,8 +1241,8 @@
       <c r="E7" s="21"/>
       <c r="F7" s="22"/>
       <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="21"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -1259,10 +1252,9 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="65"/>
+      <c r="S7" s="65"/>
     </row>
-    <row r="8" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="30"/>
       <c r="C8" s="46"/>
@@ -1270,8 +1262,8 @@
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="21"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -1281,16 +1273,15 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="65"/>
+      <c r="S8" s="65"/>
     </row>
-    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>13</v>
@@ -1305,13 +1296,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>17</v>
@@ -1320,31 +1311,28 @@
         <v>10</v>
       </c>
       <c r="M9" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="33" t="s">
+      <c r="P9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="R9" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="P9" s="33" t="s">
+      <c r="S9" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="41">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1365,11 +1353,10 @@
       <c r="O10" s="50"/>
       <c r="P10" s="50"/>
       <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="53"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="53"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1390,11 +1377,10 @@
       <c r="O11" s="54"/>
       <c r="P11" s="54"/>
       <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="57"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="57"/>
     </row>
-    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="41">
         <f t="shared" si="0"/>
@@ -1415,11 +1401,10 @@
       <c r="O12" s="58"/>
       <c r="P12" s="58"/>
       <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="61"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="61"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="36"/>
       <c r="C13" s="48"/>
@@ -1429,8 +1414,8 @@
       <c r="E13" s="38"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="40"/>
       <c r="J13" s="39"/>
       <c r="K13" s="40"/>
       <c r="L13" s="40"/>
@@ -1439,11 +1424,10 @@
       <c r="O13" s="40"/>
       <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="67"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="67"/>
     </row>
-    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="28"/>
       <c r="C14" s="49"/>
@@ -1463,15 +1447,14 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="69"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="K1:T1"/>
-    <mergeCell ref="T3:T8"/>
-    <mergeCell ref="S13:T14"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="R13:S14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74397737-0C20-4CFF-B4BE-EA33B2CF42CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Component list</t>
   </si>
@@ -62,12 +63,6 @@
   </si>
   <si>
     <t>Column=Quantity</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Column=Designator</t>
@@ -118,9 +113,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -291,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -521,22 +517,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -656,9 +641,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -725,6 +707,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,7 +761,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1066,7 +1057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1102,15 +1093,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="63"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="62"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1160,7 +1151,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="64"/>
+      <c r="S3" s="63"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1185,7 +1176,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="65"/>
+      <c r="S4" s="64"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1210,7 +1201,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="65"/>
+      <c r="S5" s="64"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1231,7 +1222,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="65"/>
+      <c r="S6" s="64"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1252,7 +1243,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="65"/>
+      <c r="S7" s="64"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1273,7 +1264,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="65"/>
+      <c r="S8" s="64"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1281,55 +1272,55 @@
         <v>8</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="I9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="33" t="s">
         <v>15</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>17</v>
       </c>
       <c r="L9" s="34" t="s">
         <v>10</v>
       </c>
       <c r="M9" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="P9" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="33" t="s">
+      <c r="R9" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" s="35" t="s">
         <v>18</v>
-      </c>
-      <c r="P9" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="S9" s="35" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1338,23 +1329,23 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="53"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="52"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -1362,23 +1353,23 @@
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="56"/>
-      <c r="S11" s="57"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="56"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1386,31 +1377,29 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="61"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="59"/>
+      <c r="S12" s="60"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="37" t="s">
-        <v>11</v>
-      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="38"/>
       <c r="F13" s="39"/>
       <c r="G13" s="40"/>
@@ -1424,16 +1413,14 @@
       <c r="O13" s="40"/>
       <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="67"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="66"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="28"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="9" t="s">
-        <v>12</v>
-      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -1447,8 +1434,8 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="69"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74397737-0C20-4CFF-B4BE-EA33B2CF42CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9551C8-A5A9-4D08-A0B8-7E18ED95A37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,28 +86,28 @@
     <t>Column=Remarks</t>
   </si>
   <si>
-    <t>Column=Reviewer Remarks</t>
-  </si>
-  <si>
     <t>Column=Item Type</t>
   </si>
   <si>
-    <t>Column=Alternate Part Number</t>
-  </si>
-  <si>
-    <t>Column=LCSC/Part Number</t>
-  </si>
-  <si>
-    <t>Column=Quantity (5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=MOQ (5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=Total Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=Unit Cost (5 Boards)</t>
+    <t>Column=Quantity(5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=MOQ(5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=AlternatePartNumber</t>
+  </si>
+  <si>
+    <t>Column=LCSCPartNumber</t>
+  </si>
+  <si>
+    <t>Column=TotalCost(5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=UnitCost(5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=ReviewerRemarks</t>
   </si>
 </sst>
 </file>
@@ -287,7 +287,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -517,29 +517,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -549,27 +579,27 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -584,7 +614,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -594,8 +624,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -607,45 +637,45 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -685,6 +715,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -709,13 +748,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1069,7 +1105,7 @@
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" customWidth="1"/>
+    <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -1093,15 +1129,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="62"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="65"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1151,7 +1187,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="63"/>
+      <c r="S3" s="66"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1176,7 +1212,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="64"/>
+      <c r="S4" s="67"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1201,7 +1237,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="64"/>
+      <c r="S5" s="67"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1222,7 +1258,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="64"/>
+      <c r="S6" s="67"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1243,7 +1279,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="64"/>
+      <c r="S7" s="67"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1264,7 +1300,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="64"/>
+      <c r="S8" s="67"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1272,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>11</v>
@@ -1290,10 +1326,10 @@
         <v>14</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>15</v>
@@ -1302,25 +1338,25 @@
         <v>10</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O9" s="33" t="s">
         <v>16</v>
       </c>
       <c r="P9" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>17</v>
       </c>
       <c r="S9" s="35" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1338,12 +1374,15 @@
       <c r="I10" s="49"/>
       <c r="J10" s="49"/>
       <c r="K10" s="49"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="49"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="51">
+        <f>L10*5</f>
+        <v>0</v>
+      </c>
       <c r="N10" s="49"/>
       <c r="O10" s="49"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
       <c r="R10" s="51"/>
       <c r="S10" s="52"/>
     </row>
@@ -1362,12 +1401,15 @@
       <c r="I11" s="53"/>
       <c r="J11" s="53"/>
       <c r="K11" s="53"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="54">
+        <f t="shared" ref="M11:M12" si="1">L11*5</f>
+        <v>0</v>
+      </c>
       <c r="N11" s="53"/>
       <c r="O11" s="53"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
       <c r="R11" s="55"/>
       <c r="S11" s="56"/>
     </row>
@@ -1386,12 +1428,15 @@
       <c r="I12" s="57"/>
       <c r="J12" s="57"/>
       <c r="K12" s="57"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="57"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="N12" s="57"/>
       <c r="O12" s="57"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
       <c r="R12" s="59"/>
       <c r="S12" s="60"/>
     </row>
@@ -1413,8 +1458,8 @@
       <c r="O13" s="40"/>
       <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="66"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="69"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1434,8 +1479,8 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="67"/>
-      <c r="S14" s="68"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9551C8-A5A9-4D08-A0B8-7E18ED95A37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8C397-ED7C-48BD-BF69-5FBA94D97ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,7 +498,20 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -507,38 +520,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -551,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -634,9 +632,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -688,40 +683,28 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -745,14 +728,23 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1129,20 +1121,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="65"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="60"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="42"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1167,7 +1159,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="43"/>
+      <c r="C3" s="42"/>
       <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1187,12 +1179,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="66"/>
+      <c r="S3" s="61"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="43"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1212,12 +1204,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="67"/>
+      <c r="S4" s="62"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="43"/>
+      <c r="C5" s="42"/>
       <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
@@ -1237,12 +1229,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="67"/>
+      <c r="S5" s="62"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="26"/>
-      <c r="C6" s="44"/>
+      <c r="C6" s="43"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
@@ -1258,12 +1250,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="67"/>
+      <c r="S6" s="62"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="45"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="22"/>
@@ -1279,12 +1271,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="67"/>
+      <c r="S7" s="62"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="46"/>
+      <c r="C8" s="45"/>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
@@ -1300,7 +1292,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="67"/>
+      <c r="S8" s="62"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1328,7 +1320,7 @@
       <c r="I9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="34" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="33" t="s">
@@ -1352,119 +1344,119 @@
       <c r="Q9" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="35" t="s">
+      <c r="R9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="S9" s="35" t="s">
+      <c r="S9" s="33" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="41">
+      <c r="B10" s="40">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="51">
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="50">
         <f>L10*5</f>
         <v>0</v>
       </c>
-      <c r="N10" s="49"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="61"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="52"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="69"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="41">
+      <c r="B11" s="40">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="54">
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="52">
         <f t="shared" ref="M11:M12" si="1">L11*5</f>
         <v>0</v>
       </c>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="62"/>
-      <c r="Q11" s="62"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="56"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="70"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="58">
+      <c r="C12" s="48"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="59"/>
-      <c r="S12" s="60"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="53"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="71"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="69"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="64"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="28"/>
-      <c r="C14" s="48"/>
+      <c r="C14" s="47"/>
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -1479,8 +1471,8 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="71"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8C397-ED7C-48BD-BF69-5FBA94D97ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22964544-53C7-491E-B86B-3D19159FE986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,25 +89,25 @@
     <t>Column=Item Type</t>
   </si>
   <si>
-    <t>Column=Quantity(5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=MOQ(5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=AlternatePartNumber</t>
-  </si>
-  <si>
-    <t>Column=LCSCPartNumber</t>
-  </si>
-  <si>
-    <t>Column=TotalCost(5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=UnitCost(5 Boards)</t>
-  </si>
-  <si>
-    <t>Column=ReviewerRemarks</t>
+    <t>Column=LCSC Part Number</t>
+  </si>
+  <si>
+    <t>Column=Alternate Part Number</t>
+  </si>
+  <si>
+    <t>Column=Reviewer Remarks</t>
+  </si>
+  <si>
+    <t>Column=UnitCost (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=TotalCost (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=MOQ (5 Boards)</t>
+  </si>
+  <si>
+    <t>Column=Quantity (5 Boards)</t>
   </si>
 </sst>
 </file>
@@ -130,6 +130,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -143,6 +144,7 @@
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -707,6 +709,21 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -730,21 +747,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1121,15 +1123,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="60"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="65"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1179,7 +1181,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="61"/>
+      <c r="S3" s="66"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1204,7 +1206,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="62"/>
+      <c r="S4" s="67"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1229,7 +1231,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="62"/>
+      <c r="S5" s="67"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1250,7 +1252,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="62"/>
+      <c r="S6" s="67"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1271,7 +1273,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="62"/>
+      <c r="S7" s="67"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1292,7 +1294,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="62"/>
+      <c r="S8" s="67"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1318,10 +1320,10 @@
         <v>14</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>15</v>
@@ -1330,16 +1332,16 @@
         <v>10</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O9" s="33" t="s">
         <v>16</v>
       </c>
       <c r="P9" s="33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="33" t="s">
         <v>23</v>
@@ -1348,7 +1350,7 @@
         <v>17</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1376,7 +1378,7 @@
       <c r="P10" s="55"/>
       <c r="Q10" s="55"/>
       <c r="R10" s="49"/>
-      <c r="S10" s="69"/>
+      <c r="S10" s="61"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -1403,7 +1405,7 @@
       <c r="P11" s="56"/>
       <c r="Q11" s="56"/>
       <c r="R11" s="52"/>
-      <c r="S11" s="70"/>
+      <c r="S11" s="62"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1427,10 +1429,10 @@
       </c>
       <c r="N12" s="53"/>
       <c r="O12" s="53"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="71"/>
+      <c r="P12" s="59"/>
+      <c r="Q12" s="59"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="63"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -1450,8 +1452,8 @@
       <c r="O13" s="39"/>
       <c r="P13" s="39"/>
       <c r="Q13" s="39"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="64"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="69"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1471,8 +1473,8 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="66"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -1,36 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22964544-53C7-491E-B86B-3D19159FE986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A63E8-8170-416A-B474-22A7C3728A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Component list</t>
   </si>
@@ -108,17 +98,24 @@
   </si>
   <si>
     <t>Column=Quantity (5 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +249,13 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -490,33 +494,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -542,6 +520,32 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -551,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -634,25 +638,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -667,10 +652,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -682,47 +663,67 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -736,17 +737,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1123,20 +1138,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="65"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="64"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="35"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1176,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="42"/>
+      <c r="C3" s="36"/>
       <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1181,12 +1196,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="66"/>
+      <c r="S3" s="65"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="36"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1206,12 +1221,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="67"/>
+      <c r="S4" s="66"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
@@ -1231,12 +1246,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="67"/>
+      <c r="S5" s="66"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="26"/>
-      <c r="C6" s="43"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
@@ -1252,12 +1267,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="67"/>
+      <c r="S6" s="66"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="44"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="22"/>
@@ -1273,12 +1288,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="67"/>
+      <c r="S7" s="66"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="45"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
@@ -1294,29 +1309,29 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="67"/>
+      <c r="S8" s="66"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="34" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="33" t="s">
@@ -1334,13 +1349,13 @@
       <c r="M9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="34" t="s">
         <v>24</v>
       </c>
       <c r="O9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="P9" s="33" t="s">
+      <c r="P9" s="34" t="s">
         <v>22</v>
       </c>
       <c r="Q9" s="33" t="s">
@@ -1353,112 +1368,126 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="40">
+      <c r="B10" s="57">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="50">
+      <c r="C10" s="42"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="41">
         <f>L10*5</f>
         <v>0</v>
       </c>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="61"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="45">
+        <f>P10*N10</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="42"/>
+      <c r="S10" s="50"/>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="40">
+      <c r="B11" s="58">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="52">
+      <c r="C11" s="44"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="43">
         <f t="shared" ref="M11:M12" si="1">L11*5</f>
         <v>0</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="62"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="46">
+        <f t="shared" ref="Q11:Q12" si="2">P11*N11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="44"/>
+      <c r="S11" s="43"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="40">
+      <c r="B12" s="59">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="54">
+      <c r="C12" s="49"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="59"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="63"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="49"/>
+      <c r="S12" s="47"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="69"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="73" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R13" s="67"/>
+      <c r="S13" s="68"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="28"/>
-      <c r="C14" s="47"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -1469,18 +1498,25 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="71"/>
+      <c r="N14" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="74" t="e">
+        <f>Q13/5</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R14" s="69"/>
+      <c r="S14" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R13:S14"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
+++ b/BOM Format/BOM Template/eSpark.Bom.Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A63E8-8170-416A-B474-22A7C3728A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA4EE11-8BB7-4AE5-BFEA-53C6E23B9654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -293,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -515,17 +515,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -555,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -635,9 +624,6 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -660,15 +646,9 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -679,9 +659,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -716,14 +693,11 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -749,19 +723,13 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1138,20 +1106,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="24"/>
-      <c r="C2" s="35"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1144,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="36"/>
+      <c r="C3" s="35"/>
       <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1196,12 +1164,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="65"/>
+      <c r="S3" s="60"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="36"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1221,12 +1189,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="66"/>
+      <c r="S4" s="61"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="36"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
@@ -1246,12 +1214,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="66"/>
+      <c r="S5" s="61"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="26"/>
-      <c r="C6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
@@ -1267,12 +1235,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="66"/>
+      <c r="S6" s="61"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="38"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="22"/>
@@ -1288,12 +1256,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="66"/>
+      <c r="S7" s="61"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="39"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="32"/>
@@ -1309,14 +1277,14 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="66"/>
+      <c r="S8" s="61"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="33" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="33" t="s">
@@ -1325,43 +1293,43 @@
       <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="33" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="H9" s="33" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="34" t="s">
+      <c r="J9" s="33" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="L9" s="33" t="s">
         <v>10</v>
       </c>
       <c r="M9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="34" t="s">
+      <c r="N9" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="33" t="s">
         <v>22</v>
       </c>
       <c r="Q9" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="34" t="s">
+      <c r="R9" s="33" t="s">
         <v>17</v>
       </c>
       <c r="S9" s="33" t="s">
@@ -1370,124 +1338,124 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="57">
+      <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="41">
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40">
         <f>L10*5</f>
         <v>0</v>
       </c>
-      <c r="N10" s="42"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="45">
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42">
         <f>P10*N10</f>
         <v>0</v>
       </c>
-      <c r="R10" s="42"/>
-      <c r="S10" s="50"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="46"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="58">
+      <c r="B11" s="54">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="43">
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41">
         <f t="shared" ref="M11:M12" si="1">L11*5</f>
         <v>0</v>
       </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="46">
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43">
         <f t="shared" ref="Q11:Q12" si="2">P11*N11</f>
         <v>0</v>
       </c>
-      <c r="R11" s="44"/>
-      <c r="S11" s="43"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="59">
+      <c r="B12" s="55">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="47">
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="49"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="62"/>
-      <c r="Q12" s="48">
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R12" s="49"/>
-      <c r="S12" s="47"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
     </row>
     <row r="13" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="71" t="s">
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="73" t="e">
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="56" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="R13" s="67"/>
-      <c r="S13" s="68"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="63"/>
     </row>
     <row r="14" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="28"/>
-      <c r="C14" s="40"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -1498,17 +1466,17 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="71" t="s">
+      <c r="N14" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="74" t="e">
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="57" t="e">
         <f>Q13/5</f>
         <v>#REF!</v>
       </c>
-      <c r="R14" s="69"/>
-      <c r="S14" s="70"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="5">
